--- a/docs/bom.xlsx
+++ b/docs/bom.xlsx
@@ -43,6 +43,9 @@
     <t xml:space="preserve">Descrizione</t>
   </si>
   <si>
+    <t xml:space="preserve">Link</t>
+  </si>
+  <si>
     <t xml:space="preserve">ToF VL53L1X</t>
   </si>
   <si>
@@ -61,28 +64,22 @@
     <t xml:space="preserve">Sensore RGB riconoscimento linea</t>
   </si>
   <si>
-    <t xml:space="preserve">silicone 15a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silicone per le ruote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4:1 Metal Gearmotor 25Dx50L mm MP 12V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motori </t>
+    <t xml:space="preserve">25mm 12V Brushless DC Gear Motor Model NFP-GM25-BL2430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motori 45:1 12V</t>
   </si>
   <si>
     <t xml:space="preserve">LiPo 3S 2200mAh 30C</t>
   </si>
   <si>
-    <t xml:space="preserve">Batteria LiPo 11.1V Nominale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L298N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor Driver</t>
+    <t xml:space="preserve">Batteria LiPo 11.1V Nominale (2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raspberry Pi Compute Module 4 8GB RAM, 8GB Flash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPU per elaborazione immagini</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALE</t>
@@ -128,16 +125,20 @@
   </si>
   <si>
     <t xml:space="preserve">Prezzo per Persona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezzo per Persona con Riserve</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0\ [$€-410];[RED]#,##0\ [$€-410]"/>
-    <numFmt numFmtId="166" formatCode="[&lt;&gt;0]&quot;SI&quot;;&quot;NO&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00\ [$€-410];[RED]#,##0.00\ [$€-410]"/>
+    <numFmt numFmtId="166" formatCode="#,##0\ [$€-410];[RED]#,##0\ [$€-410]"/>
+    <numFmt numFmtId="167" formatCode="[&lt;&gt;0]&quot;SI&quot;;&quot;NO&quot;"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -184,10 +185,11 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -223,6 +225,41 @@
       <right style="thin">
         <color rgb="FF76946A"/>
       </right>
+      <top style="thin">
+        <color rgb="FF76946A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF76946A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF76946A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF76946A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF76946A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF76946A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FF76946A"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -247,41 +284,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin">
-        <color rgb="FF76946A"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF76946A"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF76946A"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF76946A"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF76946A"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF76946A"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF76946A"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -308,7 +310,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -321,75 +323,111 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -397,71 +435,31 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -487,7 +485,6 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -501,7 +498,6 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -678,15 +674,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J23"/>
+  <dimension ref="B2:K1048576"/>
   <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.3"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -701,6 +698,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2"/>
@@ -712,399 +710,399 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <f aca="false">PRODUCT(C$5,D$5)</f>
+        <v>14.67</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <f aca="false">PRODUCT(C$5,E$5)</f>
+        <v>4.89</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9" t="str">
+        <f aca="false">HYPERLINK("https:/it.aliexpress.com/item/1005010748308679.html","AliExpress")</f>
+        <v>AliExpress</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="E6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <f aca="false">PRODUCT(C$6,D$6)</f>
+        <v>12.49</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <f aca="false">PRODUCT(C$6,E$6)</f>
+        <v>12.49</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="13" t="str">
+        <f aca="false">HYPERLINK("https://it.aliexpress.com/item/1005008036466921.html", "AliExpress")</f>
+        <v>AliExpress</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>12</v>
+        <v>1.72</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="7" t="n">
         <f aca="false">PRODUCT(C$7,D$7)</f>
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="G7" s="7" t="n">
         <f aca="false">PRODUCT(C$7,E$7)</f>
-        <v>12</v>
+        <v>1.72</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
+      <c r="K7" s="9" t="str">
+        <f aca="false">HYPERLINK("https://it.aliexpress.com/item/32956966425.html","AliExpress")</f>
+        <v>AliExpress</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="10" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>13</v>
+        <v>17.52</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">PRODUCT(C$8,D$8)</f>
-        <v>13</v>
+        <v>35.04</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">PRODUCT(C$8,E$8)</f>
-        <v>13</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
+        <v>17.52</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14" t="str">
+        <f aca="false">HYPERLINK("https://microdcmotors.com/product/25mm-brushless-dc-gear-motor-model-nfp-jga25-2430","MicroDCMotors")</f>
+        <v>MicroDCMotors</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7</v>
+        <v>17.29</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
         <f aca="false">PRODUCT(C$9,D$9)</f>
-        <v>35</v>
+        <v>17.29</v>
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">PRODUCT(C$9,E$9)</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
+      <c r="K9" s="9" t="str">
+        <f aca="false">HYPERLINK("https://chinahobbyline.com/it/products/cnhl-black-series-2200mah-11-1v-3s-30c-lipo-battery-with-xt60-plug?variant=42646803808470","ChineHobbyLine")</f>
+        <v>ChineHobbyLine</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="D10" s="12" t="n">
+      <c r="B10" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="D10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="16" t="n">
         <f aca="false">PRODUCT(C$10,D$10)</f>
-        <v>27</v>
-      </c>
-      <c r="G10" s="11" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="G10" s="16" t="n">
         <f aca="false">PRODUCT(C$10,E$10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="8" t="n">
+      <c r="H10" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18" t="str">
+        <f aca="false">HYPERLINK("https://www.ebay.it/itm/116901050395","Ebay")</f>
+        <v>Ebay</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <f aca="false">SUM(D$5:D$10)</f>
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <f aca="false">SUM(E$5:E$10)</f>
+        <v>4</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="22"/>
+      <c r="G15" s="23" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <f aca="false">IF(C17&gt;G15,TRUE())</f>
         <v>1</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <f aca="false">PRODUCT(C$11,D$11)</f>
-        <v>47.2</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <f aca="false">PRODUCT(C$11,E$11)</f>
-        <v>23.6</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="s">
+      <c r="I15" s="25" t="n">
+        <f aca="false">IF(C19&gt;G15,TRUE())</f>
+        <v>1</v>
+      </c>
+      <c r="J15" s="25"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <f aca="false">SUM(C14:C15)</f>
         <v>17</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="12" t="n">
+      <c r="E16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="27" t="n">
+        <v>200</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <f aca="false">IF(C17&gt;G16,TRUE())</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="29" t="n">
+        <f aca="false">IF(C19&gt;G16,TRUE())</f>
         <v>1</v>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <f aca="false">PRODUCT(C$12,D$12)</f>
-        <v>18</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <f aca="false">PRODUCT(C$12,E$12)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <f aca="false">PRODUCT(C$13,D$13)</f>
-        <v>7</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <f aca="false">PRODUCT(C$13,E$13)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-      <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="E15" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
+      <c r="J16" s="29"/>
     </row>
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="17" t="n">
-        <f aca="false">SUM(D$7:D$13)</f>
-        <v>14</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="J17" s="20"/>
+      <c r="B17" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <f aca="false">SUM(F$5:F$10)</f>
+        <v>196.89</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <f aca="false">SUM(E$7:E$13)</f>
-        <v>4</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24" t="n">
-        <v>150</v>
-      </c>
-      <c r="H18" s="25" t="b">
-        <f aca="false">IF(C20&gt;G18,TRUE())</f>
-        <v>1</v>
-      </c>
-      <c r="I18" s="26" t="b">
-        <f aca="false">IF(C22&gt;G18,TRUE())</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="26"/>
+      <c r="B18" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="32" t="n">
+        <f aca="false">SUM(G5:G10)</f>
+        <v>36.62</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="28" t="n">
+      <c r="B19" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="33" t="n">
         <f aca="false">SUM(C17:C18)</f>
-        <v>18</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="30" t="n">
-        <v>200</v>
-      </c>
-      <c r="H19" s="31" t="b">
-        <f aca="false">IF(C20&gt;G19,TRUE())</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="32" t="b">
-        <f aca="false">IF(C22&gt;G19,TRUE())</f>
-        <v>1</v>
-      </c>
-      <c r="J19" s="32"/>
+        <v>233.51</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="33" t="s">
-        <v>32</v>
+      <c r="B20" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C20" s="34" t="n">
-        <f aca="false">SUM(F$7:F$13)</f>
-        <v>183.2</v>
-      </c>
-      <c r="F20" s="0"/>
+        <f aca="false">QUOTIENT(C$17,3)</f>
+        <v>65</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="35" t="n">
-        <f aca="false">SUM(G7:G13)</f>
-        <v>55.6</v>
-      </c>
-      <c r="F21" s="0"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="36" t="n">
-        <f aca="false">SUM(C20:C21)</f>
-        <v>238.8</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="37" t="s">
+      <c r="B21" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="38" t="n">
-        <f aca="false">QUOTIENT(C$22,3)</f>
-        <v>79</v>
-      </c>
-    </row>
+      <c r="C21" s="36" t="n">
+        <f aca="false">QUOTIENT(C$19,3)</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E25" s="37"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B2:J3"/>
+  <mergeCells count="16">
+    <mergeCell ref="B2:K3"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="H5:J5"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="E15:J16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="E12:J13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="I16:J16"/>
   </mergeCells>
-  <conditionalFormatting sqref="I18:J19">
+  <conditionalFormatting sqref="H15:I16">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18:J19">
+  <conditionalFormatting sqref="H15:I16">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H18:H19">
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/bom.xlsx
+++ b/docs/bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t xml:space="preserve">BOM</t>
   </si>
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Sensore di distanza a luce IR </t>
   </si>
   <si>
-    <t xml:space="preserve">BNo085 imu</t>
+    <t xml:space="preserve">IMU MPU6050</t>
   </si>
   <si>
     <t xml:space="preserve">Sensore di orientamento axis XYZ</t>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t xml:space="preserve">MPU per elaborazione immagini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM25 Gear Motor Mounting Bracket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bracket per motori</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALE</t>
@@ -310,7 +316,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -384,6 +390,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -677,7 +703,7 @@
   <dimension ref="B2:K1048576"/>
   <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.96"/>
@@ -748,14 +774,14 @@
         <v>4.89</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="7" t="n">
         <f aca="false">PRODUCT(C$5,D$5)</f>
-        <v>14.67</v>
+        <v>24.45</v>
       </c>
       <c r="G5" s="7" t="n">
         <f aca="false">PRODUCT(C$5,E$5)</f>
@@ -776,21 +802,21 @@
         <v>10</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>12.49</v>
+        <v>2.11</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">PRODUCT(C$6,D$6)</f>
-        <v>12.49</v>
+        <v>4.22</v>
       </c>
       <c r="G6" s="11" t="n">
         <f aca="false">PRODUCT(C$6,E$6)</f>
-        <v>12.49</v>
+        <v>2.11</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>11</v>
@@ -798,7 +824,7 @@
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
       <c r="K6" s="13" t="str">
-        <f aca="false">HYPERLINK("https://it.aliexpress.com/item/1005008036466921.html", "AliExpress")</f>
+        <f aca="false">HYPERLINK("https://it.aliexpress.com/item/1005010057794277.html", "AliExpress")</f>
         <v>AliExpress</v>
       </c>
     </row>
@@ -841,14 +867,14 @@
         <v>17.52</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">PRODUCT(C$8,D$8)</f>
-        <v>35.04</v>
+        <v>70.08</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">PRODUCT(C$8,E$8)</f>
@@ -926,150 +952,200 @@
         <v>Ebay</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <f aca="false">D8</f>
+        <v>4</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <f aca="false">PRODUCT(C$11:D$11)</f>
+        <v>12</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <f aca="false">PRODUCT(C$11,E$11)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="23" t="str">
+        <f aca="false">HYPERLINK("https://microdcmotors.com/product/gm25-gear-motor-mounting-bracket-stand","ChineHobbyLine")</f>
+        <v>ChineHobbyLine</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="B12" s="0"/>
+      <c r="C12" s="0"/>
+      <c r="D12" s="0"/>
+      <c r="E12" s="0"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="K12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="K13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="20" t="n">
-        <f aca="false">SUM(D$5:D$10)</f>
-        <v>13</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="C14" s="2"/>
+      <c r="E14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="C16" s="25" t="n">
+        <f aca="false">SUM(D$5:D$11)</f>
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="F16" s="3"/>
+      <c r="G16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="21" t="s">
+      <c r="H16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="9" t="n">
-        <f aca="false">SUM(E$5:E$10)</f>
+      <c r="I16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <f aca="false">SUM(E$5:E$11)</f>
         <v>4</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="23" t="n">
+      <c r="E17" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="27"/>
+      <c r="G17" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="H15" s="24" t="n">
-        <f aca="false">IF(C17&gt;G15,TRUE())</f>
+      <c r="H17" s="29" t="n">
+        <f aca="false">IF(C19&gt;G17,TRUE())</f>
         <v>1</v>
       </c>
-      <c r="I15" s="25" t="n">
-        <f aca="false">IF(C19&gt;G15,TRUE())</f>
+      <c r="I17" s="30" t="n">
+        <f aca="false">IF(C21&gt;G17,TRUE())</f>
         <v>1</v>
       </c>
-      <c r="J15" s="25"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <f aca="false">SUM(C14:C15)</f>
-        <v>17</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="27" t="n">
+      <c r="J17" s="30"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <f aca="false">SUM(C16:C17)</f>
+        <v>26</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="32" t="n">
         <v>200</v>
       </c>
-      <c r="H16" s="28" t="n">
-        <f aca="false">IF(C17&gt;G16,TRUE())</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <f aca="false">IF(C19&gt;G16,TRUE())</f>
+      <c r="H18" s="33" t="n">
+        <f aca="false">IF(C19&gt;G18,TRUE())</f>
         <v>1</v>
       </c>
-      <c r="J16" s="29"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="31" t="n">
-        <f aca="false">SUM(F$5:F$10)</f>
-        <v>196.89</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="32" t="n">
+      <c r="I18" s="34" t="n">
+        <f aca="false">IF(C21&gt;G18,TRUE())</f>
+        <v>1</v>
+      </c>
+      <c r="J18" s="34"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="36" t="n">
+        <f aca="false">SUM(F$5:F$11)</f>
+        <v>245.44</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="37" t="n">
         <f aca="false">SUM(G5:G10)</f>
-        <v>36.62</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="33" t="n">
-        <f aca="false">SUM(C17:C18)</f>
-        <v>233.51</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="34" t="n">
-        <f aca="false">QUOTIENT(C$17,3)</f>
-        <v>65</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="36" t="n">
+      <c r="C21" s="38" t="n">
+        <f aca="false">SUM(C19:C20)</f>
+        <v>271.68</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="39" t="n">
         <f aca="false">QUOTIENT(C$19,3)</f>
-        <v>77</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="41" t="n">
+        <f aca="false">QUOTIENT(C$21,3)</f>
+        <v>90</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="37"/>
+      <c r="E25" s="42"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H26" s="1"/>
@@ -1078,7 +1154,7 @@
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B2:K3"/>
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="H5:J5"/>
@@ -1087,21 +1163,22 @@
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="H10:J10"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="E12:J13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="B14:C15"/>
+    <mergeCell ref="E14:J15"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="I18:J18"/>
   </mergeCells>
-  <conditionalFormatting sqref="H15:I16">
+  <conditionalFormatting sqref="H17:I18">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15:I16">
+  <conditionalFormatting sqref="H17:I18">
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>1</formula>
     </cfRule>

--- a/docs/bom.xlsx
+++ b/docs/bom.xlsx
@@ -805,14 +805,14 @@
         <v>2.11</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">PRODUCT(C$6,D$6)</f>
-        <v>4.22</v>
+        <v>2.11</v>
       </c>
       <c r="G6" s="11" t="n">
         <f aca="false">PRODUCT(C$6,E$6)</f>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C16" s="25" t="n">
         <f aca="false">SUM(D$5:D$11)</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -1080,22 +1080,22 @@
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">SUM(C16:C17)</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="32" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="H18" s="33" t="n">
         <f aca="false">IF(C19&gt;G18,TRUE())</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="34" t="n">
         <f aca="false">IF(C21&gt;G18,TRUE())</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="34"/>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C19" s="36" t="n">
         <f aca="false">SUM(F$5:F$11)</f>
-        <v>245.44</v>
+        <v>243.33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C21" s="38" t="n">
         <f aca="false">SUM(C19:C20)</f>
-        <v>271.68</v>
+        <v>269.57</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C23" s="41" t="n">
         <f aca="false">QUOTIENT(C$21,3)</f>
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/bom.xlsx
+++ b/docs/bom.xlsx
@@ -316,7 +316,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -405,7 +405,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -423,10 +423,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -980,27 +976,9 @@
       <c r="I11" s="22"/>
       <c r="J11" s="22"/>
       <c r="K11" s="23" t="str">
-        <f aca="false">HYPERLINK("https://microdcmotors.com/product/gm25-gear-motor-mounting-bracket-stand","ChineHobbyLine")</f>
-        <v>ChineHobbyLine</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0"/>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0"/>
-      <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="K12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="K13" s="0"/>
+        <f aca="false">HYPERLINK("https://microdcmotors.com/product/gm25-gear-motor-mounting-bracket-stand","MicroDCMotors")</f>
+        <v>MicroDCMotors</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
@@ -1057,25 +1035,25 @@
         <f aca="false">SUM(E$5:E$11)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28" t="n">
+      <c r="F17" s="19"/>
+      <c r="G17" s="27" t="n">
         <v>150</v>
       </c>
-      <c r="H17" s="29" t="n">
+      <c r="H17" s="28" t="n">
         <f aca="false">IF(C19&gt;G17,TRUE())</f>
         <v>1</v>
       </c>
-      <c r="I17" s="30" t="n">
+      <c r="I17" s="29" t="n">
         <f aca="false">IF(C21&gt;G17,TRUE())</f>
         <v>1</v>
       </c>
-      <c r="J17" s="30"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="30" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="14" t="n">
@@ -1086,33 +1064,33 @@
         <v>32</v>
       </c>
       <c r="F18" s="15"/>
-      <c r="G18" s="32" t="n">
+      <c r="G18" s="31" t="n">
         <v>350</v>
       </c>
-      <c r="H18" s="33" t="n">
+      <c r="H18" s="32" t="n">
         <f aca="false">IF(C19&gt;G18,TRUE())</f>
         <v>0</v>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="I18" s="33" t="n">
         <f aca="false">IF(C21&gt;G18,TRUE())</f>
         <v>0</v>
       </c>
-      <c r="J18" s="34"/>
+      <c r="J18" s="33"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="36" t="n">
+      <c r="C19" s="35" t="n">
         <f aca="false">SUM(F$5:F$11)</f>
         <v>243.33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="36" t="n">
         <f aca="false">SUM(G5:G10)</f>
         <v>26.24</v>
       </c>
@@ -1121,7 +1099,7 @@
       <c r="B21" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="38" t="n">
+      <c r="C21" s="37" t="n">
         <f aca="false">SUM(C19:C20)</f>
         <v>269.57</v>
       </c>
@@ -1130,22 +1108,22 @@
       <c r="B22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="39" t="n">
+      <c r="C22" s="38" t="n">
         <f aca="false">QUOTIENT(C$19,3)</f>
         <v>81</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C23" s="40" t="n">
         <f aca="false">QUOTIENT(C$21,3)</f>
         <v>89</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="42"/>
+      <c r="E25" s="41"/>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H26" s="1"/>
